--- a/monitor_xlsx/20260306.xlsx
+++ b/monitor_xlsx/20260306.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="總覽" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00%"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,19 +29,52 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="16"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFffffff"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF008000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFff0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="14"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <color rgb="00008000"/>
@@ -58,18 +92,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CCCCCC"/>
-        <bgColor rgb="00CCCCCC"/>
+        <fgColor rgb="FF4472c4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FFcccccc"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -77,28 +109,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -177,10 +284,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -218,69 +325,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -304,54 +413,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -361,7 +469,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -370,7 +478,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -379,7 +487,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -387,10 +495,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -419,7 +527,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -432,13 +540,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -458,404 +565,412 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
+    <col width="18.005" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>台灣股市風險監控報告 - 20260306</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>類別</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>當日數值</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>單日變動</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>5日平均</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>5日總和</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>20日平均</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>20日總和</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="20.25" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>總經</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>美債10年殖利率</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4.15%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+1.72%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>4.13%</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>總經</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>黃金指數 (GC=F)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5120.6$</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+1.09%</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>5146.1$</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>+1.60%</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+    </row>
+    <row r="6" ht="20.25" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>貨幣</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>美元/台幣匯率</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>31.91</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>+0.89%</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>現貨</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>費半指數 (SOX)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7821.76</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-1.17%</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>7514.74</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>-3.93%</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="14" t="n"/>
+    </row>
+    <row r="8" ht="20.25" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>情緒</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>恐慌指數 (VIX)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+12.29%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>29.49</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>+24.17%</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="20.25" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>原物料</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>WTI原油期貨</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>80.57$</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-0.54%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>90.9$</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>+12.21%</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="20.25" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>籌碼</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>外資現貨</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>-352.36億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>-634.09億</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>-3170.43億</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-80.78億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1615.59億</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>-97.2億</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>-1944.02億</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20.25" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>籌碼</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>投信現貨</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>67.21億</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>80.39億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>401.96億</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>71.23億</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>81.2億</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>405.98億</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="20.25" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>籌碼</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>選擇權 P/C Ratio</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>152.18%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="C12" s="20" t="n">
+        <v>1.5218</v>
+      </c>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>134.38%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="20.25" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>籌碼</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>三大法人合計</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-292.64億</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>-288.61億</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="20.25" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>籌碼</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>外資期貨未平倉</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>12061口</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>17715口</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="20.25" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2.79億</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>13.96億</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-4.51億</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-90.13億</t>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>-43.79億</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>8.17億</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>40.86億</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>-5.99億</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>-119.84億</t>
         </is>
       </c>
     </row>
@@ -863,246 +978,303 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30.005" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="20.005" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>詳細歷史統計數據</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="B1" s="14" t="n"/>
+    </row>
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>三大法人買賣超（過去20日）</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B3" s="14" t="n"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>外資 5日平均</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>-634.09億</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>外資 5日總和</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>-3170.43億</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>外資 20日平均</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-80.78億</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>-97.2億</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>外資 20日總和</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>-1615.59億</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>-1944.02億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>投信 5日平均</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>80.39億</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>81.2億</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>投信 5日總和</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>401.96億</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>405.98億</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>融資融券變化（過去20日）</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>5日平均</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.79億</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>8.17億</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>5日總和</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>13.96億</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>40.86億</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>20日平均</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>-4.51億</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>-5.99億</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>20日總和</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>-90.13億</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>-119.84億</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>期貨與選擇權（過去5日）</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>P/C Ratio 5日平均</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>134.38%</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>外資期貨淨部位 5日平均</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>17715口</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10.005" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="10.005" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
+    <col width="10.005" bestFit="1" customWidth="1" style="15" min="4" max="4"/>
+    <col width="10.005" bestFit="1" customWidth="1" style="15" min="5" max="5"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="15" min="6" max="6"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="15" min="7" max="7"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="15" min="8" max="8"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="15" min="9" max="9"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="15" min="10" max="10"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="15" min="11" max="11"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="15" min="12" max="12"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="15" min="13" max="13"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="15" min="14" max="14"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="16" min="15" max="15"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="14" min="16" max="16"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="14" min="17" max="17"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="14" min="18" max="18"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="14" min="19" max="19"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="14" min="20" max="20"/>
+    <col width="10.005" bestFit="1" customWidth="1" style="14" min="21" max="21"/>
+    <col width="12.005" bestFit="1" customWidth="1" style="14" min="22" max="22"/>
+    <col width="10.005" bestFit="1" customWidth="1" style="14" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>個股籌碼監控報告 - 20260306</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="P1" s="14" t="n"/>
+      <c r="Q1" s="14" t="n"/>
+      <c r="R1" s="14" t="n"/>
+      <c r="S1" s="14" t="n"/>
+      <c r="T1" s="14" t="n"/>
+      <c r="U1" s="14" t="n"/>
+      <c r="V1" s="14" t="n"/>
+      <c r="W1" s="14" t="n"/>
+    </row>
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+      <c r="O2" s="16" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
+      <c r="V2" s="14" t="n"/>
+      <c r="W2" s="14" t="n"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>股票代號</t>
@@ -1118,62 +1290,62 @@
           <t>市場別</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>漲跌幅(%)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>成交量(張)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>外資當日(張)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>外資5日累計</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>投信當日(張)</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>投信5日累計</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>自營商當日(張)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>融資增減(張)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>融資5日累計</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>借券增減(張)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>MA20乖離(%)</t>
         </is>
@@ -1219,801 +1391,1152 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>0050</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>0050</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="8" t="n">
         <v>76.84999999999999</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="9" t="n">
         <v>-0.71</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="10" t="n">
         <v>151611</v>
       </c>
-      <c r="H4" t="n">
+      <c r="G4" s="11" t="n">
+        <v>-75588</v>
+      </c>
+      <c r="H4" s="10" t="n">
         <v>-468801</v>
       </c>
-      <c r="J4" t="n">
+      <c r="I4" s="10" t="n">
+        <v>3300</v>
+      </c>
+      <c r="J4" s="10" t="n">
         <v>10786</v>
       </c>
-      <c r="M4" t="n">
+      <c r="K4" s="10" t="n">
+        <v>44837</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>11610</v>
+      </c>
+      <c r="M4" s="10" t="n">
         <v>48006</v>
       </c>
-      <c r="O4" t="n">
+      <c r="N4" s="10" t="n">
+        <v>-4302619</v>
+      </c>
+      <c r="O4" s="8" t="n">
         <v>-2.29</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>偏空</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>00708L</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>S&amp;P黃金正2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="11" t="n">
+        <v>-176</v>
+      </c>
+      <c r="H5" s="10" t="n">
         <v>-816</v>
       </c>
-      <c r="J5" t="n">
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="K5" s="10" t="n">
+        <v>1204</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>10103</v>
+      </c>
+      <c r="M5" s="10" t="n">
         <v>49498</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="N5" s="10" t="n">
+        <v>-27546</v>
+      </c>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>主力積極賣出</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14" t="n"/>
+      <c r="V5" s="14" t="n"/>
+      <c r="W5" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>1519</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="10" t="n">
         <v>926</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="9" t="n">
         <v>-2.63</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="10" t="n">
         <v>5461</v>
       </c>
-      <c r="H6" t="n">
+      <c r="G6" s="11" t="n">
+        <v>-979</v>
+      </c>
+      <c r="H6" s="10" t="n">
         <v>443</v>
       </c>
-      <c r="J6" t="n">
+      <c r="I6" s="10" t="n">
+        <v>-148</v>
+      </c>
+      <c r="J6" s="10" t="n">
         <v>-129</v>
       </c>
-      <c r="M6" t="n">
+      <c r="K6" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>2940</v>
+      </c>
+      <c r="M6" s="10" t="n">
         <v>14167</v>
       </c>
-      <c r="O6" t="n">
+      <c r="N6" s="10" t="n">
+        <v>-78809</v>
+      </c>
+      <c r="O6" s="8" t="n">
         <v>-6.35</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="n"/>
+      <c r="V6" s="14" t="n"/>
+      <c r="W6" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>2308</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>台達電</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="10" t="n">
         <v>1320</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="9" t="n">
         <v>-1.12</v>
       </c>
-      <c r="F7" t="n">
-        <v>10679</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="F7" s="10" t="n">
+        <v>11211</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>-777</v>
+      </c>
+      <c r="H7" s="10" t="n">
         <v>-6843</v>
       </c>
-      <c r="J7" t="n">
+      <c r="I7" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="J7" s="10" t="n">
         <v>2059</v>
       </c>
-      <c r="M7" t="n">
+      <c r="K7" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>5736</v>
+      </c>
+      <c r="M7" s="10" t="n">
         <v>30206</v>
       </c>
-      <c r="O7" t="n">
+      <c r="N7" s="10" t="n">
+        <v>-648960</v>
+      </c>
+      <c r="O7" s="8" t="n">
         <v>-2.73</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t>偏空</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Q7" s="14" t="n"/>
+      <c r="R7" s="14" t="n"/>
+      <c r="S7" s="14" t="n"/>
+      <c r="T7" s="14" t="n"/>
+      <c r="U7" s="14" t="n"/>
+      <c r="V7" s="14" t="n"/>
+      <c r="W7" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="10" t="n">
         <v>1890</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="9" t="n">
         <v>-0.53</v>
       </c>
-      <c r="F8" t="n">
-        <v>33803</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="F8" s="10" t="n">
+        <v>34307</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>-10927</v>
+      </c>
+      <c r="H8" s="10" t="n">
         <v>-95981</v>
       </c>
-      <c r="J8" t="n">
+      <c r="I8" s="10" t="n">
+        <v>946</v>
+      </c>
+      <c r="J8" s="10" t="n">
         <v>8065</v>
       </c>
-      <c r="M8" t="n">
+      <c r="K8" s="10" t="n">
+        <v>342</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>23632</v>
+      </c>
+      <c r="M8" s="10" t="n">
         <v>112428</v>
       </c>
-      <c r="O8" t="n">
+      <c r="N8" s="10" t="n">
+        <v>-6482976</v>
+      </c>
+      <c r="O8" s="8" t="n">
         <v>-2.28</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="14" t="inlineStr">
         <is>
           <t>偏空</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Q8" s="14" t="n"/>
+      <c r="R8" s="14" t="n"/>
+      <c r="S8" s="14" t="n"/>
+      <c r="T8" s="14" t="n"/>
+      <c r="U8" s="14" t="n"/>
+      <c r="V8" s="14" t="n"/>
+      <c r="W8" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>2344</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="8" t="n">
         <v>106.5</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="9" t="n">
         <v>-4.91</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="10" t="n">
         <v>122902</v>
       </c>
-      <c r="H9" t="n">
+      <c r="G9" s="12" t="n">
+        <v>5513</v>
+      </c>
+      <c r="H9" s="10" t="n">
         <v>23605</v>
       </c>
-      <c r="J9" t="n">
+      <c r="I9" s="10" t="n">
+        <v>-1859</v>
+      </c>
+      <c r="J9" s="10" t="n">
         <v>-516</v>
       </c>
-      <c r="M9" t="n">
+      <c r="K9" s="10" t="n">
+        <v>2163</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>127380</v>
+      </c>
+      <c r="M9" s="10" t="n">
         <v>652909</v>
       </c>
-      <c r="O9" t="n">
+      <c r="N9" s="10" t="n">
+        <v>-1113554</v>
+      </c>
+      <c r="O9" s="8" t="n">
         <v>-7.47</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Q9" s="14" t="n"/>
+      <c r="R9" s="14" t="n"/>
+      <c r="S9" s="14" t="n"/>
+      <c r="T9" s="14" t="n"/>
+      <c r="U9" s="14" t="n"/>
+      <c r="V9" s="14" t="n"/>
+      <c r="W9" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>2383</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>台光電</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="10" t="n">
         <v>2360</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="9" t="n">
         <v>-0.21</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="10" t="n">
         <v>2912</v>
       </c>
-      <c r="H10" t="n">
+      <c r="G10" s="11" t="n">
+        <v>-463</v>
+      </c>
+      <c r="H10" s="10" t="n">
         <v>-788</v>
       </c>
-      <c r="J10" t="n">
+      <c r="I10" s="10" t="n">
+        <v>172</v>
+      </c>
+      <c r="J10" s="10" t="n">
         <v>801</v>
       </c>
-      <c r="M10" t="n">
+      <c r="K10" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>1896</v>
+      </c>
+      <c r="M10" s="10" t="n">
         <v>9552</v>
       </c>
-      <c r="O10" t="n">
+      <c r="N10" s="10" t="n">
+        <v>-89498</v>
+      </c>
+      <c r="O10" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="14" t="inlineStr">
         <is>
           <t>偏空</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Q10" s="14" t="n"/>
+      <c r="R10" s="14" t="n"/>
+      <c r="S10" s="14" t="n"/>
+      <c r="T10" s="14" t="n"/>
+      <c r="U10" s="14" t="n"/>
+      <c r="V10" s="14" t="n"/>
+      <c r="W10" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>3661</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>世芯-KY</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="10" t="n">
         <v>3310</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="13" t="n">
         <v>1.22</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="10" t="n">
         <v>1163</v>
       </c>
-      <c r="H11" t="n">
+      <c r="G11" s="11" t="n">
+        <v>-41</v>
+      </c>
+      <c r="H11" s="10" t="n">
         <v>-389</v>
       </c>
-      <c r="J11" t="n">
+      <c r="I11" s="10" t="n">
+        <v>-22</v>
+      </c>
+      <c r="J11" s="10" t="n">
         <v>212</v>
       </c>
-      <c r="M11" t="n">
+      <c r="K11" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>5969</v>
+      </c>
+      <c r="M11" s="10" t="n">
         <v>29544</v>
       </c>
-      <c r="O11" t="n">
+      <c r="N11" s="10" t="n">
+        <v>-19735</v>
+      </c>
+      <c r="O11" s="8" t="n">
         <v>-0.75</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="14" t="inlineStr">
         <is>
           <t>偏空</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Q11" s="14" t="n"/>
+      <c r="R11" s="14" t="n"/>
+      <c r="S11" s="14" t="n"/>
+      <c r="T11" s="14" t="n"/>
+      <c r="U11" s="14" t="n"/>
+      <c r="V11" s="14" t="n"/>
+      <c r="W11" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>6442</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>光聖</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="10" t="n">
         <v>1895</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="9" t="n">
         <v>-4.53</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="10" t="n">
         <v>5169</v>
       </c>
-      <c r="H12" t="n">
+      <c r="G12" s="12" t="n">
+        <v>410</v>
+      </c>
+      <c r="H12" s="10" t="n">
         <v>-731</v>
       </c>
-      <c r="J12" t="n">
+      <c r="I12" s="10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J12" s="10" t="n">
         <v>786</v>
       </c>
-      <c r="M12" t="n">
+      <c r="K12" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>4723</v>
+      </c>
+      <c r="M12" s="10" t="n">
         <v>22002</v>
       </c>
-      <c r="O12" t="n">
+      <c r="N12" s="10" t="n">
+        <v>-19139</v>
+      </c>
+      <c r="O12" s="8" t="n">
         <v>-13.19</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="14" t="inlineStr">
         <is>
           <t>偏空</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Q12" s="14" t="n"/>
+      <c r="R12" s="14" t="n"/>
+      <c r="S12" s="14" t="n"/>
+      <c r="T12" s="14" t="n"/>
+      <c r="U12" s="14" t="n"/>
+      <c r="V12" s="14" t="n"/>
+      <c r="W12" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>3081</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5562</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="D13" s="10" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>2988</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>-233</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>-1232</v>
       </c>
-      <c r="J13" t="n">
+      <c r="I13" s="10" t="n">
+        <v>440</v>
+      </c>
+      <c r="J13" s="10" t="n">
         <v>1004</v>
       </c>
-      <c r="M13" t="n">
+      <c r="K13" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-106</v>
+      </c>
+      <c r="M13" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="O13" t="n">
+      <c r="N13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="O13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="14" t="inlineStr">
         <is>
           <t>偏空</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="14" t="n"/>
+      <c r="S13" s="14" t="n"/>
+      <c r="T13" s="14" t="n"/>
+      <c r="U13" s="14" t="n"/>
+      <c r="V13" s="14" t="n"/>
+      <c r="W13" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>威剛</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>台新科</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>287.5</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F14" t="n">
-        <v>33315</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-3230</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-3943</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1111</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="D14" s="8" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>1643</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>-226</v>
+      </c>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>-44</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>-12</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>-72</v>
+      </c>
+      <c r="N14" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="O14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="14" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="14" t="n"/>
+      <c r="S14" s="14" t="n"/>
+      <c r="T14" s="14" t="n"/>
+      <c r="U14" s="14" t="n"/>
+      <c r="V14" s="14" t="n"/>
+      <c r="W14" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>1424</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>-326</v>
+      </c>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="10" t="n">
+        <v>-674</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>181</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>-441</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="14" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="14" t="n"/>
+      <c r="S15" s="14" t="n"/>
+      <c r="T15" s="14" t="n"/>
+      <c r="U15" s="14" t="n"/>
+      <c r="V15" s="14" t="n"/>
+      <c r="W15" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1180</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>-9.92</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>440</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>-666</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>-302</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>-32</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>197</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="14" t="inlineStr">
         <is>
           <t>主力積極賣出</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Q16" s="14" t="n"/>
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="n"/>
+      <c r="T16" s="14" t="n"/>
+      <c r="U16" s="14" t="n"/>
+      <c r="V16" s="14" t="n"/>
+      <c r="W16" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>3265</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>台新科</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>耀登</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>5870</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>-411</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>707</v>
+      </c>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>4312</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>23841</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>-11543</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>-10.69</v>
+      </c>
+      <c r="P17" s="14" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+      <c r="Q17" s="14" t="n"/>
+      <c r="R17" s="14" t="n"/>
+      <c r="S17" s="14" t="n"/>
+      <c r="T17" s="14" t="n"/>
+      <c r="U17" s="14" t="n"/>
+      <c r="V17" s="14" t="n"/>
+      <c r="W17" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>6338</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>411</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>434</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>178</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>1767</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>9324</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>-140155</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+      <c r="P18" s="14" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
+      </c>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="n"/>
+      <c r="T18" s="14" t="n"/>
+      <c r="U18" s="14" t="n"/>
+      <c r="V18" s="14" t="n"/>
+      <c r="W18" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>波若威</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>138</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F15" t="n">
-        <v>951</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-226</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-72</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="D19" s="10" t="n">
+        <v>651</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>1241</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>165</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>899</v>
+      </c>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>-89</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>-571</v>
+      </c>
+      <c r="N19" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="O19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="14" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+      <c r="Q19" s="14" t="n"/>
+      <c r="R19" s="14" t="n"/>
+      <c r="S19" s="14" t="n"/>
+      <c r="T19" s="14" t="n"/>
+      <c r="U19" s="14" t="n"/>
+      <c r="V19" s="14" t="n"/>
+      <c r="W19" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>379</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-5.25</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4769</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-326</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-674</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-441</v>
-      </c>
-      <c r="O16" t="n">
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1310</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1662</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-302</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-32</v>
-      </c>
-      <c r="M17" t="n">
-        <v>197</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5870</v>
-      </c>
-      <c r="H18" t="n">
-        <v>707</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>23841</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-10.69</v>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="E20" s="10" t="n">
+        <v>3184</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>2085</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>919</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>2204</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>10586</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>-47564</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
         <is>
           <t>偏多</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1465</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6338</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-173</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-439</v>
-      </c>
-      <c r="M19" t="n">
-        <v>9488</v>
-      </c>
-      <c r="O19" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>723</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F20" t="n">
-        <v>995</v>
-      </c>
-      <c r="H20" t="n">
-        <v>899</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-571</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="P20" s="14" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+      <c r="Q20" s="14" t="n"/>
+      <c r="R20" s="14" t="n"/>
+      <c r="S20" s="14" t="n"/>
+      <c r="T20" s="14" t="n"/>
+      <c r="U20" s="14" t="n"/>
+      <c r="V20" s="14" t="n"/>
+      <c r="W20" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2023,6 +2546,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/monitor_xlsx/20260306.xlsx
+++ b/monitor_xlsx/20260306.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -203,6 +203,8 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1206,7 +1208,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.005" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2542,6 +2544,165 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>962</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>826</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>190</v>
+      </c>
+      <c r="G21" t="n">
+        <v>427</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>50</v>
+      </c>
+      <c r="K21" t="n">
+        <v>81</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>624</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2615</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>330</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-116</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-234</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1579</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <v>-161</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2162</v>
+      </c>
+      <c r="H23" t="n">
+        <v>38</v>
+      </c>
+      <c r="I23" t="n">
+        <v>924</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3199</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13356</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-106284</v>
+      </c>
+      <c r="N23" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260306.xlsx
+++ b/monitor_xlsx/20260306.xlsx
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.005" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2703,6 +2703,59 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>245</v>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12266</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="G24" t="n">
+        <v>785</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I24" t="n">
+        <v>470</v>
+      </c>
+      <c r="J24" t="n">
+        <v>268</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7141</v>
+      </c>
+      <c r="L24" t="n">
+        <v>35731</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-58835</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
